--- a/data/trans_dic/P26-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P26-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,11; 53,28</t>
+          <t>44,22; 53,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,15; 57,29</t>
+          <t>47,39; 56,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,8; 44,63</t>
+          <t>35,23; 45,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 27,52</t>
+          <t>12,91; 27,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,81; 51,94</t>
+          <t>42,17; 51,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,31; 56,83</t>
+          <t>46,93; 56,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,0; 41,75</t>
+          <t>31,91; 41,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 28,64</t>
+          <t>15,82; 29,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,69; 51,27</t>
+          <t>44,82; 50,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,81; 55,39</t>
+          <t>48,97; 55,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,56; 41,77</t>
+          <t>35,16; 41,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 25,99</t>
+          <t>16,37; 26,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,14; 37,18</t>
+          <t>30,27; 37,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,98; 42,96</t>
+          <t>34,95; 42,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,16; 34,79</t>
+          <t>27,06; 35,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 22,65</t>
+          <t>12,03; 22,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,9; 45,14</t>
+          <t>36,76; 45,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,12; 44,47</t>
+          <t>36,16; 44,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 39,72</t>
+          <t>31,56; 39,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 21,65</t>
+          <t>10,0; 21,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,16; 39,75</t>
+          <t>34,36; 39,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,74; 42,33</t>
+          <t>36,82; 42,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,46; 35,77</t>
+          <t>30,1; 35,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 19,98</t>
+          <t>12,67; 20,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,9; 26,72</t>
+          <t>19,93; 26,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,87; 35,25</t>
+          <t>27,7; 35,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,26; 28,51</t>
+          <t>21,55; 28,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 12,16</t>
+          <t>6,57; 12,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 43,44</t>
+          <t>35,56; 43,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,01; 43,99</t>
+          <t>35,86; 43,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,36</t>
+          <t>23,94; 31,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,84</t>
+          <t>11,62; 16,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,39; 34,53</t>
+          <t>29,09; 34,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,92; 38,23</t>
+          <t>32,68; 38,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 28,55</t>
+          <t>23,7; 28,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 13,48</t>
+          <t>9,79; 13,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,94; 34,78</t>
+          <t>26,27; 34,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,72; 38,04</t>
+          <t>29,66; 37,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 28,21</t>
+          <t>21,3; 28,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 72,49</t>
+          <t>10,24; 72,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,45; 47,32</t>
+          <t>38,19; 47,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,14; 51,76</t>
+          <t>42,63; 51,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,32; 32,93</t>
+          <t>25,4; 32,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 16,11</t>
+          <t>11,45; 15,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,04; 39,29</t>
+          <t>33,61; 39,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,29; 43,65</t>
+          <t>37,33; 43,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,19; 29,51</t>
+          <t>24,38; 29,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 56,34</t>
+          <t>11,99; 59,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 26,68</t>
+          <t>17,81; 26,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,39; 31,15</t>
+          <t>22,23; 31,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,82; 27,87</t>
+          <t>19,5; 27,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 15,82</t>
+          <t>10,15; 15,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,59; 37,5</t>
+          <t>28,1; 37,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,22; 41,11</t>
+          <t>31,77; 41,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,1; 29,29</t>
+          <t>21,26; 29,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 15,42</t>
+          <t>10,99; 15,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,45; 30,54</t>
+          <t>24,3; 30,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,43; 35,14</t>
+          <t>28,4; 35,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,45; 27,66</t>
+          <t>21,36; 27,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 14,75</t>
+          <t>11,3; 14,83</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 13,95</t>
+          <t>6,66; 14,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,97; 23,75</t>
+          <t>13,54; 22,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 16,67</t>
+          <t>9,03; 16,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,95</t>
+          <t>4,79; 9,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,0; 23,55</t>
+          <t>15,16; 23,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 28,73</t>
+          <t>19,13; 28,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,17; 17,96</t>
+          <t>10,21; 18,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,7</t>
+          <t>2,16; 10,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 18,0</t>
+          <t>11,91; 17,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,54; 24,76</t>
+          <t>17,53; 24,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 16,1</t>
+          <t>10,55; 16,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,75</t>
+          <t>3,19; 8,82</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 16,51</t>
+          <t>6,58; 16,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,91</t>
+          <t>6,89; 16,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,15</t>
+          <t>4,4; 10,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,11</t>
+          <t>0,5; 3,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,56; 23,3</t>
+          <t>12,48; 23,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,72; 22,4</t>
+          <t>13,82; 22,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 15,27</t>
+          <t>6,91; 14,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,08</t>
+          <t>4,2; 8,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 18,9</t>
+          <t>11,2; 18,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,79; 18,68</t>
+          <t>12,02; 18,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,2</t>
+          <t>6,52; 11,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,31</t>
+          <t>2,82; 5,28</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,86; 30,13</t>
+          <t>27,03; 30,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,4; 34,62</t>
+          <t>31,31; 34,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,62; 26,85</t>
+          <t>23,71; 26,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,44; 38,5</t>
+          <t>11,2; 36,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,83</t>
+          <t>35,37; 38,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,15; 40,41</t>
+          <t>36,9; 40,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,12; 28,2</t>
+          <t>25,04; 28,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,3</t>
+          <t>10,25; 14,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,08</t>
+          <t>31,63; 34,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,64; 37,1</t>
+          <t>34,58; 37,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,86; 27,16</t>
+          <t>24,91; 27,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,95; 26,66</t>
+          <t>11,88; 26,28</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>208838; 252249</t>
+          <t>209356; 250918</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>215319; 256160</t>
+          <t>211898; 253604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143148; 183551</t>
+          <t>144898; 185713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52202; 107512</t>
+          <t>50453; 109003</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>195014; 236612</t>
+          <t>192109; 235153</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>199535; 239696</t>
+          <t>197971; 239083</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>122118; 159327</t>
+          <t>121785; 157700</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47336; 86614</t>
+          <t>47859; 88189</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>415176; 476279</t>
+          <t>416343; 472657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>424155; 481277</t>
+          <t>425507; 480354</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274021; 331180</t>
+          <t>278743; 330971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>112693; 180185</t>
+          <t>113458; 182169</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>209874; 258861</t>
+          <t>210715; 260101</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>229325; 281640</t>
+          <t>229151; 280103</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>151224; 193690</t>
+          <t>150638; 196024</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46921; 87937</t>
+          <t>46712; 87200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>220246; 269395</t>
+          <t>219395; 269862</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>214944; 264660</t>
+          <t>215211; 266143</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>170498; 214608</t>
+          <t>170534; 213086</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51693; 107673</t>
+          <t>49739; 105934</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>441734; 514011</t>
+          <t>444327; 514259</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>459529; 529454</t>
+          <t>460555; 531318</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>334192; 392363</t>
+          <t>330252; 391399</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>108724; 176894</t>
+          <t>112182; 180999</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120159; 161292</t>
+          <t>120356; 160282</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>184883; 233865</t>
+          <t>183814; 232680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131243; 175956</t>
+          <t>133001; 175293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33594; 60647</t>
+          <t>32749; 60457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>240496; 289678</t>
+          <t>237095; 288988</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>252483; 308431</t>
+          <t>251390; 303296</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>152957; 195293</t>
+          <t>153985; 199460</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61043; 88284</t>
+          <t>60900; 86698</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>373373; 438726</t>
+          <t>369585; 439505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>449189; 521716</t>
+          <t>445887; 521232</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>299091; 359903</t>
+          <t>298745; 362669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>102191; 137852</t>
+          <t>100145; 137776</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126601; 169746</t>
+          <t>128196; 170272</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173255; 221708</t>
+          <t>172874; 220932</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126077; 168935</t>
+          <t>127560; 171803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84652; 589955</t>
+          <t>83337; 587150</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>186821; 229909</t>
+          <t>185538; 229145</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>255863; 307007</t>
+          <t>252820; 306779</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>159568; 207474</t>
+          <t>160048; 207138</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79460; 111529</t>
+          <t>79294; 110513</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>321759; 382597</t>
+          <t>327279; 388208</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>438501; 513332</t>
+          <t>438990; 511016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>297255; 362623</t>
+          <t>299602; 364210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>182990; 848508</t>
+          <t>180574; 895151</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63820; 96419</t>
+          <t>64338; 96555</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92563; 128780</t>
+          <t>91921; 131394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87666; 123258</t>
+          <t>86244; 123215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51658; 80850</t>
+          <t>51878; 79525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>103033; 140074</t>
+          <t>104958; 140793</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>137456; 175377</t>
+          <t>135522; 177042</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95832; 133044</t>
+          <t>96568; 134466</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54207; 75893</t>
+          <t>54117; 77173</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>179684; 224422</t>
+          <t>178530; 225174</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>238853; 295213</t>
+          <t>238603; 294971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>192293; 247987</t>
+          <t>191475; 244685</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>112309; 148007</t>
+          <t>113375; 148745</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17548; 36473</t>
+          <t>17410; 37902</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40559; 68968</t>
+          <t>39317; 65541</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28108; 50919</t>
+          <t>27576; 51741</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14660; 29278</t>
+          <t>15675; 30556</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41651; 65404</t>
+          <t>42099; 66624</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57368; 88158</t>
+          <t>58703; 87670</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32706; 57766</t>
+          <t>32833; 58658</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11276; 57850</t>
+          <t>11694; 57812</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63070; 97078</t>
+          <t>64220; 94100</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104762; 147865</t>
+          <t>104704; 146375</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66266; 100944</t>
+          <t>66164; 101210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27123; 75865</t>
+          <t>27679; 76532</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11283; 27674</t>
+          <t>11028; 27926</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16080; 36195</t>
+          <t>15678; 37592</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8986; 22261</t>
+          <t>9649; 22055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1030; 7468</t>
+          <t>1209; 7463</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29661; 55002</t>
+          <t>29461; 55207</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43666; 71284</t>
+          <t>43975; 72800</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21716; 47670</t>
+          <t>21562; 46321</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13630; 25527</t>
+          <t>13271; 26125</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45793; 76328</t>
+          <t>45211; 76053</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64372; 101966</t>
+          <t>65580; 100722</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36477; 64816</t>
+          <t>34626; 62721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15961; 29558</t>
+          <t>15663; 29385</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>819766; 919521</t>
+          <t>824973; 926295</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1030129; 1135805</t>
+          <t>1027083; 1135492</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>744248; 846071</t>
+          <t>747042; 847666</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>362671; 1220357</t>
+          <t>354939; 1164886</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1092109; 1200621</t>
+          <t>1093745; 1202815</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1249274; 1358923</t>
+          <t>1240770; 1360887</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>824932; 925972</t>
+          <t>822229; 926247</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>348927; 481007</t>
+          <t>344940; 485998</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1943595; 2094258</t>
+          <t>1943490; 2096193</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2301312; 2464960</t>
+          <t>2297091; 2459735</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1599733; 1747684</t>
+          <t>1603052; 1748846</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>781055; 1741870</t>
+          <t>776418; 1717584</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P26-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P26-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,22; 53,0</t>
+          <t>44,17; 53,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,39; 56,72</t>
+          <t>47,25; 57,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,23; 45,15</t>
+          <t>35,39; 45,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 27,9</t>
+          <t>13,5; 27,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,17; 51,62</t>
+          <t>42,64; 51,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,93; 56,68</t>
+          <t>47,08; 56,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,91; 41,33</t>
+          <t>31,41; 41,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,82; 29,16</t>
+          <t>14,84; 26,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,82; 50,88</t>
+          <t>44,78; 51,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,97; 55,28</t>
+          <t>49,03; 55,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,16; 41,74</t>
+          <t>34,98; 41,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 26,28</t>
+          <t>15,43; 24,86</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,27; 37,36</t>
+          <t>30,01; 37,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,95; 42,72</t>
+          <t>34,78; 42,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,06; 35,21</t>
+          <t>26,88; 34,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,03; 22,46</t>
+          <t>12,03; 22,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,76; 45,22</t>
+          <t>36,78; 44,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,16; 44,72</t>
+          <t>36,29; 44,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 39,44</t>
+          <t>31,4; 39,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 21,3</t>
+          <t>13,67; 20,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,36; 39,77</t>
+          <t>34,39; 39,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 42,48</t>
+          <t>36,75; 42,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,68</t>
+          <t>30,52; 36,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,44</t>
+          <t>14,32; 20,26</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 26,55</t>
+          <t>19,71; 26,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,7; 35,07</t>
+          <t>27,61; 34,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,55; 28,4</t>
+          <t>21,37; 29,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 12,12</t>
+          <t>6,5; 11,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,56; 43,34</t>
+          <t>36,05; 43,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,86; 43,26</t>
+          <t>36,1; 43,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,94; 31,01</t>
+          <t>23,49; 30,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 16,54</t>
+          <t>11,55; 16,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,09; 34,59</t>
+          <t>29,32; 34,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32,68; 38,2</t>
+          <t>33,01; 38,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,7; 28,77</t>
+          <t>23,68; 28,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,47</t>
+          <t>9,7; 13,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 34,89</t>
+          <t>25,83; 34,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,66; 37,9</t>
+          <t>29,38; 37,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 28,69</t>
+          <t>20,67; 28,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 72,14</t>
+          <t>9,0; 14,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,19; 47,17</t>
+          <t>38,23; 47,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,63; 51,72</t>
+          <t>43,0; 52,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 32,87</t>
+          <t>25,35; 32,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 15,96</t>
+          <t>12,32; 16,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,61; 39,86</t>
+          <t>33,31; 39,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,33; 43,45</t>
+          <t>37,42; 43,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,38; 29,63</t>
+          <t>24,14; 29,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,99; 59,43</t>
+          <t>11,4; 14,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 26,72</t>
+          <t>17,83; 26,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,23; 31,78</t>
+          <t>22,31; 31,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,5; 27,86</t>
+          <t>19,44; 27,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,56</t>
+          <t>9,5; 14,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,1; 37,7</t>
+          <t>28,19; 37,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,77; 41,5</t>
+          <t>31,85; 41,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,26; 29,6</t>
+          <t>20,69; 29,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 15,68</t>
+          <t>10,84; 15,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 30,64</t>
+          <t>24,1; 30,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,4; 35,11</t>
+          <t>28,31; 35,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,36; 27,29</t>
+          <t>21,24; 27,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,3; 14,83</t>
+          <t>11,09; 14,46</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 14,49</t>
+          <t>6,34; 13,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,54; 22,57</t>
+          <t>13,9; 23,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,94</t>
+          <t>9,06; 16,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,35</t>
+          <t>4,75; 9,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,16; 23,99</t>
+          <t>15,14; 23,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,13; 28,58</t>
+          <t>18,98; 28,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 18,23</t>
+          <t>9,9; 18,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,7</t>
+          <t>7,66; 12,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,91; 17,45</t>
+          <t>11,89; 17,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,53; 24,51</t>
+          <t>17,8; 24,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,14</t>
+          <t>10,65; 16,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,82</t>
+          <t>6,72; 9,94</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,58; 16,66</t>
+          <t>7,14; 17,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 16,52</t>
+          <t>6,68; 15,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,06</t>
+          <t>4,3; 10,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,1</t>
+          <t>0,5; 3,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 23,38</t>
+          <t>12,39; 22,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,82; 22,88</t>
+          <t>13,74; 22,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,84</t>
+          <t>7,12; 14,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,27</t>
+          <t>4,42; 8,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 18,84</t>
+          <t>11,01; 18,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 18,46</t>
+          <t>11,93; 18,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,8</t>
+          <t>6,58; 11,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,28</t>
+          <t>3,04; 5,61</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,35</t>
+          <t>26,83; 30,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,31; 34,61</t>
+          <t>31,09; 34,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,71; 26,9</t>
+          <t>23,72; 26,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 36,75</t>
+          <t>10,21; 12,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,37; 38,9</t>
+          <t>35,5; 38,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,9; 40,47</t>
+          <t>36,99; 40,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,21</t>
+          <t>25,24; 28,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,44</t>
+          <t>12,6; 14,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,12</t>
+          <t>31,74; 34,04</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,03</t>
+          <t>34,57; 37,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,91; 27,18</t>
+          <t>24,93; 27,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 26,28</t>
+          <t>11,78; 13,51</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65190</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>143095</t>
+          <t>146722</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>209356; 250918</t>
+          <t>209118; 251434</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>211898; 253604</t>
+          <t>211256; 255152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>144898; 185713</t>
+          <t>145544; 186290</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50453; 109003</t>
+          <t>52919; 106309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>192109; 235153</t>
+          <t>194246; 232897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>197971; 239083</t>
+          <t>198569; 238588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121785; 157700</t>
+          <t>119851; 158420</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47859; 88189</t>
+          <t>51972; 93847</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>416343; 472657</t>
+          <t>416028; 474009</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>425507; 480354</t>
+          <t>426078; 485170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>278743; 330971</t>
+          <t>277384; 331725</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>113458; 182169</t>
+          <t>114509; 184562</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>74490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82778</t>
+          <t>82369</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>147357</t>
+          <t>156859</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>210715; 260101</t>
+          <t>208904; 259222</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>229151; 280103</t>
+          <t>228012; 279743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150638; 196024</t>
+          <t>149641; 194384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46712; 87200</t>
+          <t>52555; 97417</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>219395; 269862</t>
+          <t>219524; 268505</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>215211; 266143</t>
+          <t>215988; 264107</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>170534; 213086</t>
+          <t>169642; 212725</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49739; 105934</t>
+          <t>66060; 100252</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>444327; 514259</t>
+          <t>444664; 515060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>460555; 531318</t>
+          <t>459689; 526008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>330252; 391399</t>
+          <t>334808; 398104</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>112182; 180999</t>
+          <t>131767; 186332</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>84154</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>119275</t>
+          <t>132970</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120356; 160282</t>
+          <t>118980; 162583</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>183814; 232680</t>
+          <t>183221; 231233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133001; 175293</t>
+          <t>131921; 179462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32749; 60457</t>
+          <t>37216; 65842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>237095; 288988</t>
+          <t>240366; 289654</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>251390; 303296</t>
+          <t>253087; 304926</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>153985; 199460</t>
+          <t>151113; 195384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60900; 86698</t>
+          <t>69591; 98157</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>369585; 439505</t>
+          <t>372564; 437757</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>445887; 521232</t>
+          <t>450395; 522970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>298745; 362669</t>
+          <t>298473; 359676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>100145; 137776</t>
+          <t>113900; 156785</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308113</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>95106</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>403219</t>
+          <t>173477</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>128196; 170272</t>
+          <t>126055; 169747</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>172874; 220932</t>
+          <t>171231; 220053</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127560; 171803</t>
+          <t>123778; 169385</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83337; 587150</t>
+          <t>55771; 88269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>185538; 229145</t>
+          <t>185715; 228969</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>252820; 306779</t>
+          <t>255065; 309563</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>160048; 207138</t>
+          <t>159764; 206204</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79294; 110513</t>
+          <t>88208; 118345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>327279; 388208</t>
+          <t>324353; 386946</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>438990; 511016</t>
+          <t>440078; 513557</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>299602; 364210</t>
+          <t>296630; 363346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>180574; 895151</t>
+          <t>152332; 194585</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64881</t>
+          <t>68076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>64967</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>129848</t>
+          <t>138550</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64338; 96555</t>
+          <t>64426; 95157</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91921; 131394</t>
+          <t>92229; 129416</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86244; 123215</t>
+          <t>85991; 122926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51878; 79525</t>
+          <t>52486; 82610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>104958; 140793</t>
+          <t>105272; 139976</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>135522; 177042</t>
+          <t>135882; 176347</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96568; 134466</t>
+          <t>93967; 134439</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54117; 77173</t>
+          <t>59392; 83145</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>178530; 225174</t>
+          <t>177112; 226877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>238603; 294971</t>
+          <t>237833; 298192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191475; 244685</t>
+          <t>190440; 244776</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113375; 148745</t>
+          <t>122083; 159078</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54769</t>
+          <t>60437</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17410; 37902</t>
+          <t>16587; 35627</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39317; 65541</t>
+          <t>40363; 68481</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27576; 51741</t>
+          <t>27680; 51102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15675; 30556</t>
+          <t>17206; 33345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42099; 66624</t>
+          <t>42058; 66368</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58703; 87670</t>
+          <t>58217; 88606</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32833; 58658</t>
+          <t>31842; 58212</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11694; 57812</t>
+          <t>27999; 45639</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64220; 94100</t>
+          <t>64115; 95043</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104704; 146375</t>
+          <t>106315; 145416</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66164; 101210</t>
+          <t>66754; 102022</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27679; 76532</t>
+          <t>48847; 72331</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>21188</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>24952</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11028; 27926</t>
+          <t>11975; 29109</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15678; 37592</t>
+          <t>15188; 36223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9649; 22055</t>
+          <t>9421; 22338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1209; 7463</t>
+          <t>1308; 8051</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29461; 55207</t>
+          <t>29250; 54021</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43975; 72800</t>
+          <t>43735; 72586</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21562; 46321</t>
+          <t>22216; 46749</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13271; 26125</t>
+          <t>15214; 29814</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45211; 76053</t>
+          <t>44467; 74889</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65580; 100722</t>
+          <t>65100; 99531</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34626; 62721</t>
+          <t>34960; 62897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15663; 29385</t>
+          <t>18456; 34085</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>586260</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>433391</t>
+          <t>467580</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1019650</t>
+          <t>833968</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>824973; 926295</t>
+          <t>818869; 923660</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1027083; 1135492</t>
+          <t>1019908; 1131297</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>747042; 847666</t>
+          <t>747300; 845332</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>354939; 1164886</t>
+          <t>326728; 413423</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1093745; 1202815</t>
+          <t>1097897; 1201372</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1240770; 1360887</t>
+          <t>1243776; 1360681</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>822229; 926247</t>
+          <t>828639; 927472</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>344940; 485998</t>
+          <t>429704; 505219</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1943490; 2096193</t>
+          <t>1949927; 2091256</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2297091; 2459735</t>
+          <t>2296675; 2459791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1603052; 1748846</t>
+          <t>1604204; 1744154</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>776418; 1717584</t>
+          <t>778596; 892654</t>
         </is>
       </c>
     </row>
